--- a/Conversation_Search/Conversation_Search_Test_Cases.xlsx
+++ b/Conversation_Search/Conversation_Search_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1854,6 +1854,628 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CS_038</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Conversation Search with Chat</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Verify search result opens correct conversation</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a contact name.
+2. Tap on result.</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Should open the correct conversation with full message history.</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CS_039</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr"/>
+      <c r="C40" s="2" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr"/>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Verify search reflects real-time new conversations</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Receive a message from a new user.
+2. Search for that user's name.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>New conversation should appear in search results immediately.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CS_040</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Regression: Conversation Search</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify search works after deleting a conversation</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Delete a conversation.
+2. Search for that contact/group.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Deleted conversation should not appear in search results.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>CS_041</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr"/>
+      <c r="C42" s="2" t="inlineStr"/>
+      <c r="D42" s="2" t="inlineStr"/>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Verify search works after leaving a group</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>1. Leave a group.
+2. Search for that group name.</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Left group should not appear in search results (or appear as 'Left').</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CS_042</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr"/>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr"/>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify search after clearing chat history</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Clear chat history of a conversation.
+2. Search for messages from that chat.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Cleared messages should not appear. Conversation may still appear but with no message matches.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>CS_043</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Security: Conversation Search</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Verify search does not expose other users' conversations</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for another user's private group name that you're not part of.</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>No results should appear for conversations user is not a participant of.</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CS_044</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr"/>
+      <c r="C45" s="2" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr"/>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in search input</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Type '&lt;img src=x onerror=alert(1)&gt;' in search bar.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Input should be sanitized. No script execution.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CS_045</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr"/>
+      <c r="C46" s="2" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify search input length limit enforced</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Try to paste 10000+ characters in search bar.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Input should be truncated or rejected. No buffer overflow or crash.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CS_046</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Edge Case: Conversation Search</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with leading/trailing spaces</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for '  John  ' (with spaces).</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Should trim spaces and return results for 'John'.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>CS_047</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr"/>
+      <c r="C48" s="2" t="inlineStr"/>
+      <c r="D48" s="2" t="inlineStr"/>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with only spaces</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>1. Type only spaces in search bar.</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Should show all conversations or ignore the search. No error.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CS_048</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr"/>
+      <c r="C49" s="2" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr"/>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with emoji in contact/group name</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Have a group named '🎮 Gamers'.
+2. Search for '🎮' or 'Gamers'.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Group should appear in results for both emoji and text search.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>CS_049</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr"/>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Verify search behavior during network fluctuation</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>1. Start searching while network is intermittent.</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>Should show loading state and handle timeouts gracefully. Retry on reconnect.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CS_050</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Boundary: Conversation Search</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with minimum 1 character</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Type a single character in search.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Should filter conversations or show minimum character requirement.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CS_051</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr"/>
+      <c r="C52" s="2" t="inlineStr"/>
+      <c r="D52" s="2" t="inlineStr"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Verify search with maximum input length</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>1. Type the maximum allowed characters in search.</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>Search should execute correctly at the boundary.</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>CS_052</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Equivalence Partitioning: Search Targets</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Verify search matches user first name</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a user's first name.</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>Conversations with matching first name should appear.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>CS_053</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr"/>
+      <c r="C54" s="2" t="inlineStr"/>
+      <c r="D54" s="2" t="inlineStr"/>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Verify search matches user last name</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a user's last name.</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>Conversations with matching last name should appear.</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>CS_054</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr"/>
+      <c r="C55" s="2" t="inlineStr"/>
+      <c r="D55" s="2" t="inlineStr"/>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Verify search matches group name</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a group name.</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>Matching group conversations should appear.</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>CS_055</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr"/>
+      <c r="C56" s="2" t="inlineStr"/>
+      <c r="D56" s="2" t="inlineStr"/>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Verify search matches message content</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>1. Search for a keyword from a message.</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing that keyword in messages should appear.</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Conversation_Search/Conversation_Search_Test_Cases.xlsx
+++ b/Conversation_Search/Conversation_Search_Test_Cases.xlsx
@@ -7,7 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Conversation Search Test Cases" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Functional" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Integration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Regression" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Security" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Edge Cases" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Boundary Values" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Equivalence Partitioning" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -433,10 +439,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="004472C4"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H56"/>
+  <dimension ref="A1:H38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -540,9 +547,9 @@
           <t>CS_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
       <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify search bar placeholder text</t>
@@ -570,9 +577,9 @@
           <t>CS_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr"/>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="2" t="inlineStr"/>
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
       <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify search bar activates on tap</t>
@@ -600,9 +607,9 @@
           <t>CS_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr"/>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
       <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify clear search input</t>
@@ -631,9 +638,9 @@
           <t>CS_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="n"/>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
       <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify cancel/close search</t>
@@ -704,9 +711,9 @@
           <t>CS_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr"/>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="n"/>
+      <c r="C8" s="2" t="n"/>
+      <c r="D8" s="2" t="n"/>
       <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Verify searching by message content</t>
@@ -734,9 +741,9 @@
           <t>CS_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr"/>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="n"/>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Verify search is case-insensitive</t>
@@ -765,9 +772,9 @@
           <t>CS_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr"/>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="n"/>
+      <c r="C10" s="2" t="n"/>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Verify real-time search results</t>
@@ -795,9 +802,9 @@
           <t>CS_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr"/>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="n"/>
+      <c r="C11" s="2" t="n"/>
+      <c r="D11" s="2" t="n"/>
       <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Verify tapping search result opens conversation</t>
@@ -911,9 +918,9 @@
           <t>CS_013</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr"/>
-      <c r="C14" s="2" t="inlineStr"/>
-      <c r="D14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
+      <c r="D14" s="2" t="n"/>
       <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Verify link results show URL preview</t>
@@ -1027,9 +1034,9 @@
           <t>CS_016</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr"/>
-      <c r="C17" s="2" t="inlineStr"/>
-      <c r="D17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
       <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Verify audio results show details</t>
@@ -1143,9 +1150,9 @@
           <t>CS_019</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr"/>
-      <c r="C20" s="2" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="n"/>
+      <c r="C20" s="2" t="n"/>
+      <c r="D20" s="2" t="n"/>
       <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Verify document results show file info</t>
@@ -1259,9 +1266,9 @@
           <t>CS_022</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr"/>
-      <c r="C23" s="2" t="inlineStr"/>
-      <c r="D23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify searching within groups filter</t>
@@ -1375,9 +1382,9 @@
           <t>CS_025</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr"/>
-      <c r="C26" s="2" t="inlineStr"/>
-      <c r="D26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="n"/>
+      <c r="C26" s="2" t="n"/>
+      <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Verify photo results show thumbnails</t>
@@ -1491,9 +1498,9 @@
           <t>CS_028</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr"/>
-      <c r="C29" s="2" t="inlineStr"/>
-      <c r="D29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="n"/>
+      <c r="C29" s="2" t="n"/>
+      <c r="D29" s="2" t="n"/>
       <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Verify video results show thumbnails</t>
@@ -1607,9 +1614,9 @@
           <t>CS_031</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr"/>
-      <c r="C32" s="2" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Verify unread count displayed in results</t>
@@ -1638,9 +1645,9 @@
           <t>CS_032</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr"/>
-      <c r="C33" s="2" t="inlineStr"/>
-      <c r="D33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="n"/>
+      <c r="C33" s="2" t="n"/>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Verify conversation removed from unread after reading</t>
@@ -1756,9 +1763,9 @@
           <t>CS_035</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr"/>
-      <c r="C36" s="2" t="inlineStr"/>
-      <c r="D36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="n"/>
+      <c r="C36" s="2" t="n"/>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Verify search results count</t>
@@ -1830,9 +1837,9 @@
           <t>CS_037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr"/>
-      <c r="C38" s="2" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n"/>
       <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
@@ -1854,623 +1861,1025 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0070AD47"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CS_038</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C39" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Integration: Conversation Search with Chat</t>
         </is>
       </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify search result opens correct conversation</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Search for a contact name.
 2. Tap on result.</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should open the correct conversation with full message history.</t>
         </is>
       </c>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CS_039</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr"/>
-      <c r="C40" s="2" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr"/>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify search reflects real-time new conversations</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Receive a message from a new user.
 2. Search for that user's name.</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>New conversation should appear in search results immediately.</t>
         </is>
       </c>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFC000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CS_040</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Regression: Conversation Search</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify search works after deleting a conversation</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Delete a conversation.
 2. Search for that contact/group.</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Deleted conversation should not appear in search results.</t>
         </is>
       </c>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CS_041</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr"/>
-      <c r="C42" s="2" t="inlineStr"/>
-      <c r="D42" s="2" t="inlineStr"/>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify search works after leaving a group</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Search for that group name.</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Left group should not appear in search results (or appear as 'Left').</t>
         </is>
       </c>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CS_042</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr"/>
-      <c r="C43" s="2" t="inlineStr"/>
-      <c r="D43" s="2" t="inlineStr"/>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify search after clearing chat history</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Clear chat history of a conversation.
 2. Search for messages from that chat.</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Cleared messages should not appear. Conversation may still appear but with no message matches.</t>
         </is>
       </c>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FF0000"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CS_043</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C44" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Security: Conversation Search</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify search does not expose other users' conversations</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Search for another user's private group name that you're not part of.</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>No results should appear for conversations user is not a participant of.</t>
         </is>
       </c>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CS_044</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr"/>
-      <c r="C45" s="2" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr"/>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify XSS prevention in search input</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Type '&lt;img src=x onerror=alert(1)&gt;' in search bar.</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Input should be sanitized. No script execution.</t>
         </is>
       </c>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CS_045</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr"/>
-      <c r="C46" s="2" t="inlineStr"/>
-      <c r="D46" s="2" t="inlineStr"/>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify search input length limit enforced</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Try to paste 10000+ characters in search bar.</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Input should be truncated or rejected. No buffer overflow or crash.</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00ED7D31"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CS_046</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C47" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Edge Case: Conversation Search</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify search with leading/trailing spaces</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Search for '  John  ' (with spaces).</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should trim spaces and return results for 'John'.</t>
         </is>
       </c>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CS_047</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr"/>
-      <c r="C48" s="2" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr"/>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify search with only spaces</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Type only spaces in search bar.</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Should show all conversations or ignore the search. No error.</t>
         </is>
       </c>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CS_048</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr"/>
-      <c r="C49" s="2" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr"/>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify search with emoji in contact/group name</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Have a group named '🎮 Gamers'.
 2. Search for '🎮' or 'Gamers'.</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Group should appear in results for both emoji and text search.</t>
         </is>
       </c>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CS_049</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C50" s="2" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr"/>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify search behavior during network fluctuation</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Start searching while network is intermittent.</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Should show loading state and handle timeouts gracefully. Retry on reconnect.</t>
         </is>
       </c>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="007030A0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CS_050</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C51" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Boundary: Conversation Search</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify search with minimum 1 character</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Type a single character in search.</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Should filter conversations or show minimum character requirement.</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CS_051</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr"/>
-      <c r="C52" s="2" t="inlineStr"/>
-      <c r="D52" s="2" t="inlineStr"/>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify search with maximum input length</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Type the maximum allowed characters in search.</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Search should execute correctly at the boundary.</t>
         </is>
       </c>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="0000B0F0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>TestCase_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Sentiment</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Test Scenario</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Precondition</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Steps</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Expected Results</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Priority / Severity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>CS_052</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C53" s="2" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Search Targets</t>
         </is>
       </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>Verify search matches user first name</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>1. Search for a user's first name.</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr">
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>Conversations with matching first name should appear.</t>
         </is>
       </c>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>CS_053</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr"/>
-      <c r="C54" s="2" t="inlineStr"/>
-      <c r="D54" s="2" t="inlineStr"/>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>Verify search matches user last name</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>1. Search for a user's last name.</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>Conversations with matching last name should appear.</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>CS_054</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr"/>
-      <c r="C55" s="2" t="inlineStr"/>
-      <c r="D55" s="2" t="inlineStr"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="B4" s="2" t="n"/>
+      <c r="C4" s="2" t="n"/>
+      <c r="D4" s="2" t="n"/>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Verify search matches group name</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>1. Search for a group name.</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Matching group conversations should appear.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>CS_055</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr"/>
-      <c r="C56" s="2" t="inlineStr"/>
-      <c r="D56" s="2" t="inlineStr"/>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="B5" s="2" t="n"/>
+      <c r="C5" s="2" t="n"/>
+      <c r="D5" s="2" t="n"/>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Verify search matches message content</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>1. Search for a keyword from a message.</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>Conversations containing that keyword in messages should appear.</t>
         </is>
       </c>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>

--- a/Conversation_Search/Conversation_Search_Test_Cases.xlsx
+++ b/Conversation_Search/Conversation_Search_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -828,546 +828,374 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CS_011</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Verify Text Message Search</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Verify no results for non-matching search</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1. Type a random string that doesn't match any conversation or message.</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display (e.g., 'No results found').</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="n"/>
+      <c r="B12" s="2" t="n"/>
+      <c r="C12" s="2" t="n"/>
+      <c r="D12" s="2" t="n"/>
+      <c r="E12" s="2" t="n"/>
+      <c r="F12" s="2" t="n"/>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CS_012</t>
+          <t>CS_011</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Verify Links Search</t>
+          <t>Verify Text Message Search</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and has messages with links</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify links filter in conversation search</t>
+          <t>Verify no results for non-matching search</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Links' filter.</t>
+          <t>1. Type a random string that doesn't match any conversation or message.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Conversations containing link messages should display.</t>
+          <t>Empty state should display (e.g., 'No results found').</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CS_013</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="n"/>
       <c r="B14" s="2" t="n"/>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="n"/>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="n"/>
+      <c r="H14" s="2" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>CS_012</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Verify Links Search</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has messages with links</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Verify links filter in conversation search</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Links' filter.</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing link messages should display.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>CS_013</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n"/>
+      <c r="C16" s="2" t="n"/>
+      <c r="D16" s="2" t="n"/>
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Verify link results show URL preview</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1. Filter by Links.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>Results should show link URL, preview title, sender, and conversation name.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CS_014</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Links Search</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no link messages</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for links filter</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Links' filter.</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no links found.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CS_015</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Search</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has audio messages</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Verify audio filter in conversation search</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1. Open conversation search.
-2. Select 'Audio' filter.</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Conversations containing audio messages should display.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CS_016</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="n"/>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="n"/>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="n"/>
+      <c r="H17" s="2" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>CS_014</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Verify Links Search</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no link messages</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for links filter</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Links' filter.</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no links found.</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n"/>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
+      <c r="D19" s="2" t="n"/>
+      <c r="E19" s="2" t="n"/>
+      <c r="F19" s="2" t="n"/>
+      <c r="G19" s="2" t="n"/>
+      <c r="H19" s="2" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>CS_015</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Search</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has audio messages</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio filter in conversation search</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Audio' filter.</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing audio messages should display.</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>CS_016</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n"/>
+      <c r="C21" s="2" t="n"/>
+      <c r="D21" s="2" t="n"/>
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Verify audio results show details</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>1. Filter by Audio.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>Results should show audio duration, sender, conversation name, and date.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="n"/>
+      <c r="B22" s="2" t="n"/>
+      <c r="C22" s="2" t="n"/>
+      <c r="D22" s="2" t="n"/>
+      <c r="E22" s="2" t="n"/>
+      <c r="F22" s="2" t="n"/>
+      <c r="G22" s="2" t="n"/>
+      <c r="H22" s="2" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>CS_017</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
         <is>
           <t>Verify Audio Search</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>User is logged in with no audio messages</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Verify empty state for audio filter</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>1. Select 'Audio' filter.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>Empty state should display indicating no audio messages found.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="n"/>
+      <c r="B24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n"/>
+      <c r="E24" s="2" t="n"/>
+      <c r="F24" s="2" t="n"/>
+      <c r="G24" s="2" t="n"/>
+      <c r="H24" s="2" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>CS_018</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>Verify Documents Search</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>User is logged in and has document messages</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Verify documents filter in conversation search</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Documents' filter.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>Conversations containing document messages should display.</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CS_019</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n"/>
-      <c r="C20" s="2" t="n"/>
-      <c r="D20" s="2" t="n"/>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Verify document results show file info</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter by Documents.
-2. Observe results.</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>Results should show file name, type, size, sender, and date.</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CS_020</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Verify Documents Search</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no document messages</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for documents filter</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Documents' filter.</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no documents found.</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CS_021</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Verify Groups Search</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and is part of groups</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Verify groups filter in conversation search</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>1. Open conversation search.
-2. Select 'Groups' filter.</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Only group conversations should display in results.</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CS_022</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Verify searching within groups filter</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Groups' filter.
-2. Type a group name.</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>Matching group conversations should filter and display.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CS_023</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Verify Groups Search</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no group conversations</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for groups filter</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Groups' filter.</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no groups found.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CS_024</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify Photos Search</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has image messages</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Verify photos filter in conversation search</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>1. Open conversation search.
-2. Select 'Photos' filter.</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>Conversations containing image messages should display.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -1379,7 +1207,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CS_025</t>
+          <t>CS_019</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1387,18 +1215,18 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify photo results show thumbnails</t>
+          <t>Verify document results show file info</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Filter by Photos.
+          <t>1. Filter by Documents.
 2. Observe results.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Results should show image thumbnails, sender, conversation name, and date.</t>
+          <t>Results should show file name, type, size, sender, and date.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1408,198 +1236,133 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CS_026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Verify Photos Search</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no image messages</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for photos filter</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Photos' filter.</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no photos found.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="n"/>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="2" t="n"/>
+      <c r="E27" s="2" t="n"/>
+      <c r="F27" s="2" t="n"/>
+      <c r="G27" s="2" t="n"/>
+      <c r="H27" s="2" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CS_027</t>
+          <t>CS_020</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Verify Videos Search</t>
+          <t>Verify Documents Search</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and has video messages</t>
+          <t>User is logged in with no document messages</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify videos filter in conversation search</t>
+          <t>Verify empty state for documents filter</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Videos' filter.</t>
+          <t>1. Select 'Documents' filter.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Conversations containing video messages should display.</t>
+          <t>Empty state should display indicating no documents found.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CS_028</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="n"/>
       <c r="B29" s="2" t="n"/>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Verify video results show thumbnails</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter by Videos.
-2. Observe results.</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>Results should show video thumbnails with play icon, duration, sender, and date.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="E29" s="2" t="n"/>
+      <c r="F29" s="2" t="n"/>
+      <c r="G29" s="2" t="n"/>
+      <c r="H29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CS_029</t>
+          <t>CS_021</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Verify Videos Search</t>
+          <t>Verify Groups Search</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User is logged in with no video messages</t>
+          <t>User is logged in and is part of groups</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify empty state for videos filter</t>
+          <t>Verify groups filter in conversation search</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Videos' filter.</t>
+          <t>1. Open conversation search.
+2. Select 'Groups' filter.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display indicating no videos found.</t>
+          <t>Only group conversations should display in results.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CS_030</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>Verify Unread Filter</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has unread conversations</t>
-        </is>
-      </c>
+          <t>CS_022</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n"/>
+      <c r="C31" s="2" t="n"/>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify unread filter shows unread conversations</t>
+          <t>Verify searching within groups filter</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Unread' filter.</t>
+          <t>1. Select 'Groups' filter.
+2. Type a group name.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Only conversations with unread messages should display.</t>
+          <t>Matching group conversations should filter and display.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -1609,114 +1372,71 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CS_031</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="n"/>
       <c r="B32" s="2" t="n"/>
       <c r="C32" s="2" t="n"/>
       <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>Verify unread count displayed in results</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter by Unread.
-2. Observe results.</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>Each conversation should show the unread message count badge.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
+      <c r="E32" s="2" t="n"/>
+      <c r="F32" s="2" t="n"/>
+      <c r="G32" s="2" t="n"/>
+      <c r="H32" s="2" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>CS_032</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="n"/>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n"/>
+          <t>CS_023</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Verify Groups Search</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no group conversations</t>
+        </is>
+      </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Verify conversation removed from unread after reading</t>
+          <t>Verify empty state for groups filter</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1. Filter by Unread.
-2. Open and read a conversation.
-3. Go back to unread filter.</t>
+          <t>1. Select 'Groups' filter.</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>Read conversation should no longer appear in unread filter results.</t>
+          <t>Empty state should display indicating no groups found.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CS_033</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Verify Unread Filter</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with all conversations read</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for unread filter</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Unread' filter.</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no unread conversations.</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="n"/>
+      <c r="B34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n"/>
+      <c r="E34" s="2" t="n"/>
+      <c r="F34" s="2" t="n"/>
+      <c r="G34" s="2" t="n"/>
+      <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CS_034</t>
+          <t>CS_024</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -1726,29 +1446,28 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Verify Conversation Search General</t>
+          <t>Verify Photos Search</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>User is logged in</t>
+          <t>User is logged in and has image messages</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify switching between search filters</t>
+          <t>Verify photos filter in conversation search</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Photos' filter.
-2. Switch to 'Videos'.
-3. Switch to 'Unread'.</t>
+          <t>1. Open conversation search.
+2. Select 'Photos' filter.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Results should update correctly when switching between filters.</t>
+          <t>Conversations containing image messages should display.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -1760,7 +1479,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CS_035</t>
+          <t>CS_025</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
@@ -1768,94 +1487,545 @@
       <c r="D36" s="2" t="n"/>
       <c r="E36" s="2" t="inlineStr">
         <is>
+          <t>Verify photo results show thumbnails</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>1. Filter by Photos.
+2. Observe results.</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Results should show image thumbnails, sender, conversation name, and date.</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n"/>
+      <c r="B37" s="2" t="n"/>
+      <c r="C37" s="2" t="n"/>
+      <c r="D37" s="2" t="n"/>
+      <c r="E37" s="2" t="n"/>
+      <c r="F37" s="2" t="n"/>
+      <c r="G37" s="2" t="n"/>
+      <c r="H37" s="2" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>CS_026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Verify Photos Search</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no image messages</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for photos filter</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Photos' filter.</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no photos found.</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n"/>
+      <c r="B39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n"/>
+      <c r="E39" s="2" t="n"/>
+      <c r="F39" s="2" t="n"/>
+      <c r="G39" s="2" t="n"/>
+      <c r="H39" s="2" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>CS_027</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Verify Videos Search</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has video messages</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Verify videos filter in conversation search</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Videos' filter.</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing video messages should display.</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>CS_028</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="2" t="n"/>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Verify video results show thumbnails</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>1. Filter by Videos.
+2. Observe results.</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>Results should show video thumbnails with play icon, duration, sender, and date.</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n"/>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="2" t="n"/>
+      <c r="E42" s="2" t="n"/>
+      <c r="F42" s="2" t="n"/>
+      <c r="G42" s="2" t="n"/>
+      <c r="H42" s="2" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>CS_029</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Verify Videos Search</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no video messages</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for videos filter</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Videos' filter.</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no videos found.</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n"/>
+      <c r="B44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n"/>
+      <c r="E44" s="2" t="n"/>
+      <c r="F44" s="2" t="n"/>
+      <c r="G44" s="2" t="n"/>
+      <c r="H44" s="2" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>CS_030</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Verify Unread Filter</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has unread conversations</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread filter shows unread conversations</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Unread' filter.</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Only conversations with unread messages should display.</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>CS_031</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread count displayed in results</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>1. Filter by Unread.
+2. Observe results.</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>Each conversation should show the unread message count badge.</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>High / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>CS_032</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Verify conversation removed from unread after reading</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>1. Filter by Unread.
+2. Open and read a conversation.
+3. Go back to unread filter.</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>Read conversation should no longer appear in unread filter results.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n"/>
+      <c r="B48" s="2" t="n"/>
+      <c r="C48" s="2" t="n"/>
+      <c r="D48" s="2" t="n"/>
+      <c r="E48" s="2" t="n"/>
+      <c r="F48" s="2" t="n"/>
+      <c r="G48" s="2" t="n"/>
+      <c r="H48" s="2" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>CS_033</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Verify Unread Filter</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with all conversations read</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for unread filter</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Unread' filter.</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no unread conversations.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n"/>
+      <c r="B50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="n"/>
+      <c r="G50" s="2" t="n"/>
+      <c r="H50" s="2" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>CS_034</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Verify Conversation Search General</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching between search filters</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Photos' filter.
+2. Switch to 'Videos'.
+3. Switch to 'Unread'.</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>Results should update correctly when switching between filters.</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>CS_035</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n"/>
+      <c r="C52" s="2" t="n"/>
+      <c r="D52" s="2" t="n"/>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>Verify search results count</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>1. Perform a search.
 2. Observe result count.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr">
         <is>
           <t>Number of matching results should display.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="n"/>
+      <c r="B53" s="2" t="n"/>
+      <c r="C53" s="2" t="n"/>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="n"/>
+      <c r="G53" s="2" t="n"/>
+      <c r="H53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>CS_036</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C54" s="2" t="inlineStr">
         <is>
           <t>Verify Conversation Search General</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Verify search fails gracefully without network</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to search.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr">
         <is>
           <t>Appropriate error message should display or cached results should show.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>CS_037</t>
         </is>
       </c>
-      <c r="B38" s="2" t="n"/>
-      <c r="C38" s="2" t="n"/>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="B55" s="2" t="n"/>
+      <c r="C55" s="2" t="n"/>
+      <c r="D55" s="2" t="n"/>
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>1. Type special characters in search bar (e.g., '@#$%&amp;').</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr">
         <is>
           <t>Search should handle gracefully without crash or error.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
@@ -2355,7 +2525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2514,34 +2684,44 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CS_049</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="n"/>
+      <c r="B5" s="2" t="n"/>
       <c r="C5" s="2" t="n"/>
       <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
+      <c r="G5" s="2" t="n"/>
+      <c r="H5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>CS_049</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n"/>
+      <c r="D6" s="2" t="n"/>
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Verify search behavior during network fluctuation</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>1. Start searching while network is intermittent.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>Should show loading state and handle timeouts gracefully. Retry on reconnect.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Medium / High</t>
         </is>

--- a/Conversation_Search/Conversation_Search_Test_Cases.xlsx
+++ b/Conversation_Search/Conversation_Search_Test_Cases.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -828,49 +828,71 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="n"/>
-      <c r="B12" s="2" t="n"/>
-      <c r="C12" s="2" t="n"/>
-      <c r="D12" s="2" t="n"/>
-      <c r="E12" s="2" t="n"/>
-      <c r="F12" s="2" t="n"/>
-      <c r="G12" s="2" t="n"/>
-      <c r="H12" s="2" t="n"/>
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>CS_012</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Verify Links Search</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has messages with links</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Verify links filter in conversation search</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Links' filter.</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing link messages should display.</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>CS_011</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Verify Text Message Search</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
+          <t>CS_013</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n"/>
+      <c r="C13" s="2" t="n"/>
+      <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Verify no results for non-matching search</t>
+          <t>Verify link results show URL preview</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1. Type a random string that doesn't match any conversation or message.</t>
+          <t>1. Filter by Links.
+2. Observe results.</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display (e.g., 'No results found').</t>
+          <t>Results should show link URL, preview title, sender, and conversation name.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -880,155 +902,231 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n"/>
-      <c r="B14" s="2" t="n"/>
-      <c r="C14" s="2" t="n"/>
-      <c r="D14" s="2" t="n"/>
-      <c r="E14" s="2" t="n"/>
-      <c r="F14" s="2" t="n"/>
-      <c r="G14" s="2" t="n"/>
-      <c r="H14" s="2" t="n"/>
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>CS_015</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Search</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has audio messages</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Verify audio filter in conversation search</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Audio' filter.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing audio messages should display.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>CS_012</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Verify Links Search</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has messages with links</t>
-        </is>
-      </c>
+          <t>CS_016</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n"/>
+      <c r="C15" s="2" t="n"/>
+      <c r="D15" s="2" t="n"/>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Verify links filter in conversation search</t>
+          <t>Verify audio results show details</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Links' filter.</t>
+          <t>1. Filter by Audio.
+2. Observe results.</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Conversations containing link messages should display.</t>
+          <t>Results should show audio duration, sender, conversation name, and date.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>CS_013</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
+          <t>CS_018</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Verify Documents Search</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has document messages</t>
+        </is>
+      </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Verify link results show URL preview</t>
+          <t>Verify documents filter in conversation search</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1. Filter by Links.
-2. Observe results.</t>
+          <t>1. Open conversation search.
+2. Select 'Documents' filter.</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>Results should show link URL, preview title, sender, and conversation name.</t>
+          <t>Conversations containing document messages should display.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>CS_019</t>
+        </is>
+      </c>
       <c r="B17" s="2" t="n"/>
       <c r="C17" s="2" t="n"/>
       <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="n"/>
-      <c r="F17" s="2" t="n"/>
-      <c r="G17" s="2" t="n"/>
-      <c r="H17" s="2" t="n"/>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Verify document results show file info</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1. Filter by Documents.
+2. Observe results.</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>Results should show file name, type, size, sender, and date.</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>CS_014</t>
+          <t>CS_021</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Verify Links Search</t>
+          <t>Verify Groups Search</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>User is logged in with no link messages</t>
+          <t>User is logged in and is part of groups</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Verify empty state for links filter</t>
+          <t>Verify groups filter in conversation search</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Links' filter.</t>
+          <t>1. Open conversation search.
+2. Select 'Groups' filter.</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display indicating no links found.</t>
+          <t>Only group conversations should display in results.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="n"/>
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>CS_022</t>
+        </is>
+      </c>
       <c r="B19" s="2" t="n"/>
       <c r="C19" s="2" t="n"/>
       <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="n"/>
-      <c r="F19" s="2" t="n"/>
-      <c r="G19" s="2" t="n"/>
-      <c r="H19" s="2" t="n"/>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Verify searching within groups filter</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Groups' filter.
+2. Type a group name.</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>Matching group conversations should filter and display.</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>CS_015</t>
+          <t>CS_024</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1038,28 +1136,28 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Verify Audio Search</t>
+          <t>Verify Photos Search</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and has audio messages</t>
+          <t>User is logged in and has image messages</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Verify audio filter in conversation search</t>
+          <t>Verify photos filter in conversation search</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
           <t>1. Open conversation search.
-2. Select 'Audio' filter.</t>
+2. Select 'Photos' filter.</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>Conversations containing audio messages should display.</t>
+          <t>Conversations containing image messages should display.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1071,7 +1169,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>CS_016</t>
+          <t>CS_025</t>
         </is>
       </c>
       <c r="B21" s="2" t="n"/>
@@ -1079,18 +1177,18 @@
       <c r="D21" s="2" t="n"/>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Verify audio results show details</t>
+          <t>Verify photo results show thumbnails</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1. Filter by Audio.
+          <t>1. Filter by Photos.
 2. Observe results.</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Results should show audio duration, sender, conversation name, and date.</t>
+          <t>Results should show image thumbnails, sender, conversation name, and date.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1100,49 +1198,71 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="n"/>
-      <c r="B22" s="2" t="n"/>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n"/>
-      <c r="E22" s="2" t="n"/>
-      <c r="F22" s="2" t="n"/>
-      <c r="G22" s="2" t="n"/>
-      <c r="H22" s="2" t="n"/>
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>CS_027</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Verify Videos Search</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has video messages</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Verify videos filter in conversation search</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Videos' filter.</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>Conversations containing video messages should display.</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>CS_017</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Verify Audio Search</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no audio messages</t>
-        </is>
-      </c>
+          <t>CS_028</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n"/>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Verify empty state for audio filter</t>
+          <t>Verify video results show thumbnails</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Audio' filter.</t>
+          <t>1. Filter by Videos.
+2. Observe results.</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display indicating no audio messages found.</t>
+          <t>Results should show video thumbnails with play icon, duration, sender, and date.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1152,62 +1272,83 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="n"/>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-      <c r="G24" s="2" t="n"/>
-      <c r="H24" s="2" t="n"/>
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>CS_030</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Verify Unread Filter</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in and has unread conversations</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Verify unread filter shows unread conversations</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1. Open conversation search.
+2. Select 'Unread' filter.</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>Only conversations with unread messages should display.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>CS_018</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Verify Documents Search</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has document messages</t>
-        </is>
-      </c>
+          <t>CS_031</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n"/>
+      <c r="C25" s="2" t="n"/>
+      <c r="D25" s="2" t="n"/>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Verify documents filter in conversation search</t>
+          <t>Verify unread count displayed in results</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Documents' filter.</t>
+          <t>1. Filter by Unread.
+2. Observe results.</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>Conversations containing document messages should display.</t>
+          <t>Each conversation should show the unread message count badge.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>CS_019</t>
+          <t>CS_032</t>
         </is>
       </c>
       <c r="B26" s="2" t="n"/>
@@ -1215,75 +1356,99 @@
       <c r="D26" s="2" t="n"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Verify document results show file info</t>
+          <t>Verify conversation removed from unread after reading</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1. Filter by Documents.
-2. Observe results.</t>
+          <t>1. Filter by Unread.
+2. Open and read a conversation.
+3. Go back to unread filter.</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>Results should show file name, type, size, sender, and date.</t>
+          <t>Read conversation should no longer appear in unread filter results.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="n"/>
-      <c r="B27" s="2" t="n"/>
-      <c r="C27" s="2" t="n"/>
-      <c r="D27" s="2" t="n"/>
-      <c r="E27" s="2" t="n"/>
-      <c r="F27" s="2" t="n"/>
-      <c r="G27" s="2" t="n"/>
-      <c r="H27" s="2" t="n"/>
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>CS_034</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Verify Conversation Search General</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Verify switching between search filters</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Photos' filter.
+2. Switch to 'Videos'.
+3. Switch to 'Unread'.</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>Results should update correctly when switching between filters.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>High / High</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>CS_020</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Verify Documents Search</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no document messages</t>
-        </is>
-      </c>
+          <t>CS_035</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n"/>
+      <c r="C28" s="2" t="n"/>
+      <c r="D28" s="2" t="n"/>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Verify empty state for documents filter</t>
+          <t>Verify search results count</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Documents' filter.</t>
+          <t>1. Perform a search.
+2. Observe result count.</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display indicating no documents found.</t>
+          <t>Number of matching results should display.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>Low / Low</t>
         </is>
       </c>
     </row>
@@ -1300,148 +1465,222 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>CS_021</t>
+          <t>CS_011</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Verify Groups Search</t>
+          <t>Verify Text Message Search</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and is part of groups</t>
+          <t>User is logged in</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Verify groups filter in conversation search</t>
+          <t>Verify no results for non-matching search</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Groups' filter.</t>
+          <t>1. Type a random string that doesn't match any conversation or message.</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>Only group conversations should display in results.</t>
+          <t>Empty state should display (e.g., 'No results found').</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>CS_022</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
+          <t>CS_014</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Verify Links Search</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no link messages</t>
+        </is>
+      </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Verify searching within groups filter</t>
+          <t>Verify empty state for links filter</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Groups' filter.
-2. Type a group name.</t>
+          <t>1. Select 'Links' filter.</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>Matching group conversations should filter and display.</t>
+          <t>Empty state should display indicating no links found.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="n"/>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-      <c r="F32" s="2" t="n"/>
-      <c r="G32" s="2" t="n"/>
-      <c r="H32" s="2" t="n"/>
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>CS_017</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Verify Audio Search</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no audio messages</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for audio filter</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Audio' filter.</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no audio messages found.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>CS_020</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Verify Documents Search</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no document messages</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for documents filter</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Documents' filter.</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no documents found.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
           <t>CS_023</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
         <is>
           <t>Verify Groups Search</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>User is logged in with no group conversations</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Verify empty state for groups filter</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>1. Select 'Groups' filter.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t>Empty state should display indicating no groups found.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n"/>
-      <c r="B34" s="2" t="n"/>
-      <c r="C34" s="2" t="n"/>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-      <c r="F34" s="2" t="n"/>
-      <c r="G34" s="2" t="n"/>
-      <c r="H34" s="2" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>CS_024</t>
+          <t>CS_026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -1451,54 +1690,64 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>User is logged in and has image messages</t>
+          <t>User is logged in with no image messages</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Verify photos filter in conversation search</t>
+          <t>Verify empty state for photos filter</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1. Open conversation search.
-2. Select 'Photos' filter.</t>
+          <t>1. Select 'Photos' filter.</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>Conversations containing image messages should display.</t>
+          <t>Empty state should display indicating no photos found.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>High / High</t>
+          <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>CS_025</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="n"/>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n"/>
+          <t>CS_029</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Verify Videos Search</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with no video messages</t>
+        </is>
+      </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Verify photo results show thumbnails</t>
+          <t>Verify empty state for videos filter</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1. Filter by Photos.
-2. Observe results.</t>
+          <t>1. Select 'Videos' filter.</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>Results should show image thumbnails, sender, conversation name, and date.</t>
+          <t>Empty state should display indicating no videos found.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -1508,19 +1757,51 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="n"/>
-      <c r="B37" s="2" t="n"/>
-      <c r="C37" s="2" t="n"/>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-      <c r="F37" s="2" t="n"/>
-      <c r="G37" s="2" t="n"/>
-      <c r="H37" s="2" t="n"/>
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>CS_033</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Verify Unread Filter</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in with all conversations read</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Verify empty state for unread filter</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>1. Select 'Unread' filter.</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Empty state should display indicating no unread conversations.</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>Medium / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>CS_026</t>
+          <t>CS_036</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -1530,502 +1811,61 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Verify Photos Search</t>
+          <t>Verify Conversation Search General</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>User is logged in with no image messages</t>
+          <t>User is logged in, network disconnected</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Verify empty state for photos filter</t>
+          <t>Verify search fails gracefully without network</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>1. Select 'Photos' filter.</t>
+          <t>1. Disconnect network.
+2. Try to search.</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>Empty state should display indicating no photos found.</t>
+          <t>Appropriate error message should display or cached results should show.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Medium / Medium</t>
+          <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="n"/>
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>CS_037</t>
+        </is>
+      </c>
       <c r="B39" s="2" t="n"/>
       <c r="C39" s="2" t="n"/>
       <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-      <c r="F39" s="2" t="n"/>
-      <c r="G39" s="2" t="n"/>
-      <c r="H39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CS_027</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>Verify Videos Search</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has video messages</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>Verify videos filter in conversation search</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>1. Open conversation search.
-2. Select 'Videos' filter.</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>Conversations containing video messages should display.</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CS_028</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n"/>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>Verify video results show thumbnails</t>
-        </is>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter by Videos.
-2. Observe results.</t>
-        </is>
-      </c>
-      <c r="G41" s="2" t="inlineStr">
-        <is>
-          <t>Results should show video thumbnails with play icon, duration, sender, and date.</t>
-        </is>
-      </c>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="n"/>
-      <c r="B42" s="2" t="n"/>
-      <c r="C42" s="2" t="n"/>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-      <c r="F42" s="2" t="n"/>
-      <c r="G42" s="2" t="n"/>
-      <c r="H42" s="2" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CS_029</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>Verify Videos Search</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with no video messages</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for videos filter</t>
-        </is>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Videos' filter.</t>
-        </is>
-      </c>
-      <c r="G43" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no videos found.</t>
-        </is>
-      </c>
-      <c r="H43" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n"/>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-      <c r="E44" s="2" t="n"/>
-      <c r="F44" s="2" t="n"/>
-      <c r="G44" s="2" t="n"/>
-      <c r="H44" s="2" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CS_030</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>Verify Unread Filter</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and has unread conversations</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>Verify unread filter shows unread conversations</t>
-        </is>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>1. Open conversation search.
-2. Select 'Unread' filter.</t>
-        </is>
-      </c>
-      <c r="G45" s="2" t="inlineStr">
-        <is>
-          <t>Only conversations with unread messages should display.</t>
-        </is>
-      </c>
-      <c r="H45" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CS_031</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n"/>
-      <c r="C46" s="2" t="n"/>
-      <c r="D46" s="2" t="n"/>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>Verify unread count displayed in results</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter by Unread.
-2. Observe results.</t>
-        </is>
-      </c>
-      <c r="G46" s="2" t="inlineStr">
-        <is>
-          <t>Each conversation should show the unread message count badge.</t>
-        </is>
-      </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>High / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CS_032</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n"/>
-      <c r="C47" s="2" t="n"/>
-      <c r="D47" s="2" t="n"/>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>Verify conversation removed from unread after reading</t>
-        </is>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>1. Filter by Unread.
-2. Open and read a conversation.
-3. Go back to unread filter.</t>
-        </is>
-      </c>
-      <c r="G47" s="2" t="inlineStr">
-        <is>
-          <t>Read conversation should no longer appear in unread filter results.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="n"/>
-      <c r="B48" s="2" t="n"/>
-      <c r="C48" s="2" t="n"/>
-      <c r="D48" s="2" t="n"/>
-      <c r="E48" s="2" t="n"/>
-      <c r="F48" s="2" t="n"/>
-      <c r="G48" s="2" t="n"/>
-      <c r="H48" s="2" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CS_033</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>Verify Unread Filter</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in with all conversations read</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>Verify empty state for unread filter</t>
-        </is>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Unread' filter.</t>
-        </is>
-      </c>
-      <c r="G49" s="2" t="inlineStr">
-        <is>
-          <t>Empty state should display indicating no unread conversations.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>Medium / Medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="2" t="n"/>
-      <c r="B50" s="2" t="n"/>
-      <c r="C50" s="2" t="n"/>
-      <c r="D50" s="2" t="n"/>
-      <c r="E50" s="2" t="n"/>
-      <c r="F50" s="2" t="n"/>
-      <c r="G50" s="2" t="n"/>
-      <c r="H50" s="2" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CS_034</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>Positive</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Verify Conversation Search General</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>Verify switching between search filters</t>
-        </is>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>1. Select 'Photos' filter.
-2. Switch to 'Videos'.
-3. Switch to 'Unread'.</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>Results should update correctly when switching between filters.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CS_035</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n"/>
-      <c r="C52" s="2" t="n"/>
-      <c r="D52" s="2" t="n"/>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Verify search results count</t>
-        </is>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>1. Perform a search.
-2. Observe result count.</t>
-        </is>
-      </c>
-      <c r="G52" s="2" t="inlineStr">
-        <is>
-          <t>Number of matching results should display.</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>Low / Low</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="2" t="n"/>
-      <c r="B53" s="2" t="n"/>
-      <c r="C53" s="2" t="n"/>
-      <c r="D53" s="2" t="n"/>
-      <c r="E53" s="2" t="n"/>
-      <c r="F53" s="2" t="n"/>
-      <c r="G53" s="2" t="n"/>
-      <c r="H53" s="2" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CS_036</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Verify Conversation Search General</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, network disconnected</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>Verify search fails gracefully without network</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>1. Disconnect network.
-2. Try to search.</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>Appropriate error message should display or cached results should show.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>High / High</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CS_037</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n"/>
-      <c r="C55" s="2" t="n"/>
-      <c r="D55" s="2" t="n"/>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Verify search with special characters</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>1. Type special characters in search bar (e.g., '@#$%&amp;').</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr">
         <is>
           <t>Search should handle gracefully without crash or error.</t>
         </is>
       </c>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>

--- a/Conversation_Search/Conversation_Search_Test_Cases.xlsx
+++ b/Conversation_Search/Conversation_Search_Test_Cases.xlsx
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -36,8 +36,18 @@
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -48,6 +58,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="004472C4"/>
         <bgColor rgb="004472C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+        <bgColor rgb="001F4E79"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,13 +85,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -443,1431 +465,2312 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H39"/>
+  <dimension ref="A1:H60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CS_001</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Verify Conversation Search UI</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in and on Chats tab</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify search bar is visible on Chats tab</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Navigate to Chats tab.
 2. Observe top of conversation list.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Search bar/input field should be visible at the top of the conversation list.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CS_002</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify search bar placeholder text</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Observe search bar without typing.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Placeholder text should display (e.g., 'Search conversations...').</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CS_003</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify search bar activates on tap</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Tap on search bar.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Search bar should become active with cursor. Keyboard should appear (mobile).</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CS_004</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify clear search input</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Type text in search bar.
 2. Click clear (X) button.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Search text should clear and full conversation list should restore.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CS_005</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n"/>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify cancel/close search</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Activate search bar.
 2. Click cancel or press back.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>Search should close and return to normal conversation list view.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>CS_006</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Verify Text Message Search</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>User is logged in with existing conversations</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify searching by contact/group name</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>1. Type a contact or group name in search bar.</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>Matching conversations should filter and display in results.</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>CS_007</t>
         </is>
       </c>
-      <c r="B8" s="2" t="n"/>
-      <c r="C8" s="2" t="n"/>
-      <c r="D8" s="2" t="n"/>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>Verify searching by message content</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="4" t="inlineStr">
         <is>
           <t>1. Type a keyword from a message in search bar.</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>Conversations containing messages with that keyword should display.</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CS_008</t>
         </is>
       </c>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify search is case-insensitive</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Search for 'John'.
 2. Search for 'john'.</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Both searches should return the same results.</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>CS_009</t>
         </is>
       </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="n"/>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>Verify real-time search results</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="4" t="inlineStr">
         <is>
           <t>1. Start typing in search bar character by character.</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>Results should filter in real-time as user types.</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="H10" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>CS_010</t>
         </is>
       </c>
-      <c r="B11" s="2" t="n"/>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="n"/>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Verify tapping search result opens conversation</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>1. Search for a conversation.
 2. Tap on a result.</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>Should open the matching conversation with message history.</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>CS_012</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Verify Links Search</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has messages with links</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>Verify links filter in conversation search</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F12" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Links' filter.</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>Conversations containing link messages should display.</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>CS_013</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="2" t="n"/>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>Verify link results show URL preview</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Links.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>Results should show link URL, preview title, sender, and conversation name.</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>CS_015</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>Verify Audio Search</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has audio messages</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>Verify audio filter in conversation search</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Audio' filter.</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>Conversations containing audio messages should display.</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H14" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>CS_016</t>
         </is>
       </c>
-      <c r="B15" s="2" t="n"/>
-      <c r="C15" s="2" t="n"/>
-      <c r="D15" s="2" t="n"/>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>Verify audio results show details</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Audio.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
         <is>
           <t>Results should show audio duration, sender, conversation name, and date.</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>CS_018</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>Verify Documents Search</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has document messages</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>Verify documents filter in conversation search</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Documents' filter.</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
         <is>
           <t>Conversations containing document messages should display.</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>CS_019</t>
         </is>
       </c>
-      <c r="B17" s="2" t="n"/>
-      <c r="C17" s="2" t="n"/>
-      <c r="D17" s="2" t="n"/>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>Verify document results show file info</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Documents.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>Results should show file name, type, size, sender, and date.</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>CS_021</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>Verify Groups Search</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>User is logged in and is part of groups</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>Verify groups filter in conversation search</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F18" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Groups' filter.</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>Only group conversations should display in results.</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>CS_022</t>
         </is>
       </c>
-      <c r="B19" s="2" t="n"/>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n"/>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>Verify searching within groups filter</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Groups' filter.
 2. Type a group name.</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>Matching group conversations should filter and display.</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H19" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CS_024</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>Verify Photos Search</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has image messages</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>Verify photos filter in conversation search</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F20" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Photos' filter.</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>Conversations containing image messages should display.</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="H20" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>CS_025</t>
         </is>
       </c>
-      <c r="B21" s="2" t="n"/>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n"/>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="inlineStr">
         <is>
           <t>Verify photo results show thumbnails</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F21" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Photos.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>Results should show image thumbnails, sender, conversation name, and date.</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="H21" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>CS_027</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
+      <c r="C22" s="4" t="inlineStr">
         <is>
           <t>Verify Videos Search</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has video messages</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E22" s="4" t="inlineStr">
         <is>
           <t>Verify videos filter in conversation search</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F22" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Videos' filter.</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>Conversations containing video messages should display.</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="H22" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>CS_028</t>
         </is>
       </c>
-      <c r="B23" s="2" t="n"/>
-      <c r="C23" s="2" t="n"/>
-      <c r="D23" s="2" t="n"/>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="inlineStr">
         <is>
           <t>Verify video results show thumbnails</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Videos.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>Results should show video thumbnails with play icon, duration, sender, and date.</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H23" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>CS_030</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C24" s="2" t="inlineStr">
+      <c r="C24" s="4" t="inlineStr">
         <is>
           <t>Verify Unread Filter</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D24" s="4" t="inlineStr">
         <is>
           <t>User is logged in and has unread conversations</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E24" s="4" t="inlineStr">
         <is>
           <t>Verify unread filter shows unread conversations</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F24" s="4" t="inlineStr">
         <is>
           <t>1. Open conversation search.
 2. Select 'Unread' filter.</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>Only conversations with unread messages should display.</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="H24" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>CS_031</t>
         </is>
       </c>
-      <c r="B25" s="2" t="n"/>
-      <c r="C25" s="2" t="n"/>
-      <c r="D25" s="2" t="n"/>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="inlineStr">
         <is>
           <t>Verify unread count displayed in results</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F25" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Unread.
 2. Observe results.</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>Each conversation should show the unread message count badge.</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="H25" s="4" t="inlineStr">
         <is>
           <t>High / Medium</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>CS_032</t>
         </is>
       </c>
-      <c r="B26" s="2" t="n"/>
-      <c r="C26" s="2" t="n"/>
-      <c r="D26" s="2" t="n"/>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="B26" s="4" t="n"/>
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="inlineStr">
         <is>
           <t>Verify conversation removed from unread after reading</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F26" s="4" t="inlineStr">
         <is>
           <t>1. Filter by Unread.
 2. Open and read a conversation.
 3. Go back to unread filter.</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>Read conversation should no longer appear in unread filter results.</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="H26" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>CS_034</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B27" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
+      <c r="C27" s="4" t="inlineStr">
         <is>
           <t>Verify Conversation Search General</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="D27" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E27" s="4" t="inlineStr">
         <is>
           <t>Verify switching between search filters</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F27" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Photos' filter.
 2. Switch to 'Videos'.
 3. Switch to 'Unread'.</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
         <is>
           <t>Results should update correctly when switching between filters.</t>
         </is>
       </c>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="H27" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>CS_035</t>
         </is>
       </c>
-      <c r="B28" s="2" t="n"/>
-      <c r="C28" s="2" t="n"/>
-      <c r="D28" s="2" t="n"/>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="inlineStr">
         <is>
           <t>Verify search results count</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F28" s="4" t="inlineStr">
         <is>
           <t>1. Perform a search.
 2. Observe result count.</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
         <is>
           <t>Number of matching results should display.</t>
         </is>
       </c>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="H28" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="n"/>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="2" t="n"/>
-      <c r="E29" s="2" t="n"/>
-      <c r="F29" s="2" t="n"/>
-      <c r="G29" s="2" t="n"/>
-      <c r="H29" s="2" t="n"/>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>CS_037</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>Verify search with special characters</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>1. Type special characters in search bar (e.g., '@#$%&amp;').</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>Search should handle gracefully without crash or error.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Low / Medium</t>
+        </is>
+      </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>CS_056</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>Combined Search</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>Search component open</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>Verify search returns both conversations and messages</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter search text
+2. Check results</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>Both conversation and message results shown</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>CS_057</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>Combined Search - Conversations Section</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>Search results visible</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversations section in results</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for text
+2. Check conversations section</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>Matching conversations listed with avatars and names</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>CS_058</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>Combined Search - Messages Section</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>Search results visible</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>Verify messages section in results</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for text
+2. Check messages section</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>Matching messages listed with sender and content</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>CS_059</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Conversations</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>Verify conversations filter toggle</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Conversations filter chip</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only conversations</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CS_060</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Unread</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>Verify unread filter toggle</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Unread filter chip</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only unread conversations</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>CS_061</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Groups</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>Verify groups filter toggle</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Groups filter chip</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only group conversations</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>CS_062</t>
+        </is>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Photos</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>Verify photos filter toggle</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Photos filter chip</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only photo messages</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>CS_063</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Videos</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>Verify videos filter toggle</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Videos filter chip</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only video messages</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>CS_064</t>
+        </is>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Documents</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>Verify documents filter toggle</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Documents filter chip</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only document messages</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>CS_065</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Audio</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>Verify audio filter toggle</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Audio filter chip</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only audio messages</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>CS_066</t>
+        </is>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>Filter Toggling - Links</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>Filters visible</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>Verify links filter toggle</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>1. Click Links filter chip</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>Results filtered to show only link messages</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>CS_067</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Messages Filter - In User Chat</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>uid prop set</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Verify search within specific user chat</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>1. Set uid prop
+2. Search for text</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>Results limited to messages with that user</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>CS_068</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>Messages Filter - In Group Chat</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>guid prop set</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Verify search within specific group chat</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>1. Set guid prop
+2. Search for text</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>Results limited to messages in that group</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CS_069</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>Filter Deselect</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>Filter active</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Verify deselecting a filter</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>1. Click active filter chip again</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>Filter removed, results show all types again</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>CS_070</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Search Debounce</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>User typing search</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Verify search debounces input (500ms)</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>1. Type rapidly in search
+2. Check API calls</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>Search triggers after 500ms pause, not on every keystroke</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>CS_071</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>Click Conversation Result</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>Conversation result visible</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Verify clicking conversation navigates to chat</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>1. Click on conversation result</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>Chat opens for selected conversation</t>
+        </is>
+      </c>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>CS_072</t>
+        </is>
+      </c>
+      <c r="B46" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C46" s="4" t="inlineStr">
+        <is>
+          <t>Click Message Result</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>Message result visible</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>Verify clicking message navigates to message</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>1. Click on message result</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>Chat opens and scrolls to the specific message</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="47"/>
+    <row r="48">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>CS_011</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B48" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
+      <c r="C48" s="4" t="inlineStr">
         <is>
           <t>Verify Text Message Search</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D48" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E48" s="4" t="inlineStr">
         <is>
           <t>Verify no results for non-matching search</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F48" s="4" t="inlineStr">
         <is>
           <t>1. Type a random string that doesn't match any conversation or message.</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="G48" s="4" t="inlineStr">
         <is>
           <t>Empty state should display (e.g., 'No results found').</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="H48" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>CS_014</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
+      <c r="C49" s="4" t="inlineStr">
         <is>
           <t>Verify Links Search</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no link messages</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E49" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for links filter</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F49" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Links' filter.</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="G49" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no links found.</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="H49" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>CS_017</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Verify Audio Search</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no audio messages</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for audio filter</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F50" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Audio' filter.</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no audio messages found.</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H50" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>CS_020</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B51" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
+      <c r="C51" s="4" t="inlineStr">
         <is>
           <t>Verify Documents Search</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="D51" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no document messages</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E51" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for documents filter</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F51" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Documents' filter.</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr">
+      <c r="G51" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no documents found.</t>
         </is>
       </c>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="H51" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>CS_023</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B52" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
+      <c r="C52" s="4" t="inlineStr">
         <is>
           <t>Verify Groups Search</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D52" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no group conversations</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E52" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for groups filter</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F52" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Groups' filter.</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="G52" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no groups found.</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="H52" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>CS_026</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B53" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
+      <c r="C53" s="4" t="inlineStr">
         <is>
           <t>Verify Photos Search</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D53" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no image messages</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E53" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for photos filter</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F53" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Photos' filter.</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr">
+      <c r="G53" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no photos found.</t>
         </is>
       </c>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="H53" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>CS_029</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B54" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
+      <c r="C54" s="4" t="inlineStr">
         <is>
           <t>Verify Videos Search</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="D54" s="4" t="inlineStr">
         <is>
           <t>User is logged in with no video messages</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E54" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for videos filter</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F54" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Videos' filter.</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no videos found.</t>
         </is>
       </c>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="H54" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>CS_033</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B55" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
+      <c r="C55" s="4" t="inlineStr">
         <is>
           <t>Verify Unread Filter</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="D55" s="4" t="inlineStr">
         <is>
           <t>User is logged in with all conversations read</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E55" s="4" t="inlineStr">
         <is>
           <t>Verify empty state for unread filter</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F55" s="4" t="inlineStr">
         <is>
           <t>1. Select 'Unread' filter.</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>Empty state should display indicating no unread conversations.</t>
         </is>
       </c>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="H55" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>CS_036</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
+      <c r="B56" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C38" s="2" t="inlineStr">
+      <c r="C56" s="4" t="inlineStr">
         <is>
           <t>Verify Conversation Search General</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="D56" s="4" t="inlineStr">
         <is>
           <t>User is logged in, network disconnected</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E56" s="4" t="inlineStr">
         <is>
           <t>Verify search fails gracefully without network</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F56" s="4" t="inlineStr">
         <is>
           <t>1. Disconnect network.
 2. Try to search.</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>Appropriate error message should display or cached results should show.</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="H56" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CS_037</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n"/>
-      <c r="C39" s="2" t="n"/>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>Verify search with special characters</t>
-        </is>
-      </c>
-      <c r="F39" s="2" t="inlineStr">
-        <is>
-          <t>1. Type special characters in search bar (e.g., '@#$%&amp;').</t>
-        </is>
-      </c>
-      <c r="G39" s="2" t="inlineStr">
-        <is>
-          <t>Search should handle gracefully without crash or error.</t>
-        </is>
-      </c>
-      <c r="H39" s="2" t="inlineStr">
-        <is>
-          <t>Low / Medium</t>
+    <row r="57">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>CS_073</t>
+        </is>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Empty Search Results</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>No matching results</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty state for no results</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for non-existent text</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>Empty state view with 'No results found' message</t>
+        </is>
+      </c>
+      <c r="H57" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>CS_074</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Search Error</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>Network error during search</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Verify error state handling</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect network
+2. Search</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>Error state view displayed</t>
+        </is>
+      </c>
+      <c r="H58" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>CS_075</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Filter Mutual Exclusion</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>Content filter + conversation filter</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Verify mutually exclusive filters</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>1. Select Photos filter
+2. Try to select Conversations</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>Conversation filter replaces content filter or vice versa</t>
+        </is>
+      </c>
+      <c r="H59" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>CS_076</t>
+        </is>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Empty Search Text</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>No text entered</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Verify initial state with no search</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>1. Open search with empty input</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>Initial view shown (not results)</t>
+        </is>
+      </c>
+      <c r="H60" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1879,136 +2782,311 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="0070AD47"/>
+    <tabColor rgb="00548235"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CS_038</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Integration: Conversation Search with Chat</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify search result opens correct conversation</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Search for a contact name.
 2. Tap on result.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should open the correct conversation with full message history.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CS_039</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify search reflects real-time new conversations</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Receive a message from a new user.
 2. Search for that user's name.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>New conversation should appear in search results immediately.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CS_077</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Search + Navigation</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Search result clicked</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify navigation from search to chat</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for message
+2. Click result
+3. Check chat</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Chat opens at correct message with highlight</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CS_078</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Filter + Pagination</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Many results with filter</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify pagination works with active filter</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Apply filter
+2. Scroll to load more</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>More filtered results load on scroll</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CS_079</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Search + Receipts</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>hideReceipts=false</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify receipts shown in search results</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Search messages
+2. Check receipt indicators</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Read/delivered indicators visible in results</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CS_080</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Search + Deleted Message</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Message deleted after search</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify handling of deleted message in results</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Search
+2. Delete a result message
+3. Click it</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate handling (removed or error)</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2020,167 +3098,298 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FFC000"/>
+    <tabColor rgb="00BF8F00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CS_040</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Regression: Conversation Search</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify search works after deleting a conversation</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Delete a conversation.
 2. Search for that contact/group.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Deleted conversation should not appear in search results.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CS_041</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify search works after leaving a group</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Leave a group.
 2. Search for that group name.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Left group should not appear in search results (or appear as 'Left').</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CS_042</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify search after clearing chat history</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Clear chat history of a conversation.
 2. Search for messages from that chat.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Cleared messages should not appear. Conversation may still appear but with no message matches.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CS_081</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Filter After Clear Search</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Search cleared</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify filters reset after clearing search</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Search with filter
+2. Clear search text</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Filters and results reset</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CS_082</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Search After New Message</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>New message received</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify search includes new messages</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Receive new message
+2. Search for its content</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>New message appears in search results</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CS_083</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Filter After Reconnect</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Network reconnected</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify filters work after reconnection</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Disconnect
+2. Reconnect
+3. Apply filter</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Filters work correctly after reconnection</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2192,164 +3401,249 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00FF0000"/>
+    <tabColor rgb="00C00000"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
+        <is>
+          <t>CS_044</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="inlineStr">
+        <is>
+          <t>Verify XSS prevention in search input</t>
+        </is>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>1. Type '&lt;img src=x onerror=alert(1)&gt;' in search bar.</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Input should be sanitized. No script execution.</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>High / Critical</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>CS_045</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Verify search input length limit enforced</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>1. Try to paste 10000+ characters in search bar.</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Input should be truncated or rejected. No buffer overflow or crash.</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CS_084</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Search Auth Required</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>Valid session</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify search requires authentication</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Attempt search without login</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Search fails with auth error</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="5"/>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>CS_043</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>Security: Conversation Search</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Verify search does not expose other users' conversations</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>1. Search for another user's private group name that you're not part of.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>No results should appear for conversations user is not a participant of.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H6" s="4" t="inlineStr">
         <is>
           <t>High / Critical</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CS_044</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CS_085</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Search XSS</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Malicious search query</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Verify XSS prevention in search input</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1. Type '&lt;img src=x onerror=alert(1)&gt;' in search bar.</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Input should be sanitized. No script execution.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>High / Critical</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CS_045</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>Verify search input length limit enforced</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1. Try to paste 10000+ characters in search bar.</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Input should be truncated or rejected. No buffer overflow or crash.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>Medium / High</t>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter &lt;script&gt;alert('xss')&lt;/script&gt; in search</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Script sanitized, no execution</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
     </row>
@@ -2365,205 +3659,364 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CS_046</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Edge Case: Conversation Search</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify search with leading/trailing spaces</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Search for '  John  ' (with spaces).</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should trim spaces and return results for 'John'.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Low / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CS_047</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify search with only spaces</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Type only spaces in search bar.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Should show all conversations or ignore the search. No error.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CS_048</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify search with emoji in contact/group name</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Have a group named '🎮 Gamers'.
 2. Search for '🎮' or 'Gamers'.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Group should appear in results for both emoji and text search.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="n"/>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="n"/>
-      <c r="F5" s="2" t="n"/>
-      <c r="G5" s="2" t="n"/>
-      <c r="H5" s="2" t="n"/>
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CS_086</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Search Special Characters</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Query with special chars</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify search handles special characters</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for '@#$%'</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Results shown or empty state, no crash</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CS_087</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Search Unicode/Emoji</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Query with emoji</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify search handles unicode/emoji</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for emoji character</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Matching messages with emoji found</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CS_088</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Multiple Filters Active</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>2+ filters selected</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify multiple filter combination</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Select Photos and Videos filters</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>Results show both photos and videos</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>CS_049</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Negative</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n"/>
-      <c r="D6" s="2" t="n"/>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Verify search behavior during network fluctuation</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>1. Start searching while network is intermittent.</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>Should show loading state and handle timeouts gracefully. Retry on reconnect.</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>Medium / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CS_089</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Very Long Search Query</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>500+ character query</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify long query handling</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter very long search text</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Appropriate handling (truncated or error)</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2579,130 +4032,260 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CS_050</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Boundary: Conversation Search</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify search with minimum 1 character</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Type a single character in search.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Should filter conversations or show minimum character requirement.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>Medium / Medium</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CS_051</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify search with maximum input length</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Type the maximum allowed characters in search.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Search should execute correctly at the boundary.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>Low / Low</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>CS_090</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Search Min 1 Char</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>1 character query</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>Verify search with minimum input</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter 1 character
+2. Wait for debounce</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>Search executes with 1 character</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>CS_091</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Search Results Limit</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Many matching results</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>Verify initial results limit</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>1. Search common term
+2. Check result count</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>Limited results shown with 'See more' option</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CS_092</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Search Empty String</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Empty/whitespace query</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify empty string not searched</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Enter only spaces
+2. Check</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>No search executed, initial view shown</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2718,190 +4301,359 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="45" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
     <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>TestCase_ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>Sentiment</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>Test Scenario</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>Precondition</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Test Case</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>Steps</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>Expected Results</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Priority / Severity</t>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Priority/Severity</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>CS_052</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="4" t="inlineStr">
         <is>
           <t>Positive</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="4" t="inlineStr">
         <is>
           <t>Equivalence Partitioning: Search Targets</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="4" t="inlineStr">
         <is>
           <t>User is logged in</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>Verify search matches user first name</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="4" t="inlineStr">
         <is>
           <t>1. Search for a user's first name.</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>Conversations with matching first name should appear.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>CS_053</t>
         </is>
       </c>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>Verify search matches user last name</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>1. Search for a user's last name.</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>Conversations with matching last name should appear.</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>CS_054</t>
         </is>
       </c>
-      <c r="B4" s="2" t="n"/>
-      <c r="C4" s="2" t="n"/>
-      <c r="D4" s="2" t="n"/>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>Verify search matches group name</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>1. Search for a group name.</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>Matching group conversations should appear.</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>CS_055</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n"/>
-      <c r="C5" s="2" t="n"/>
-      <c r="D5" s="2" t="n"/>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>Verify search matches message content</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>1. Search for a keyword from a message.</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>Conversations containing that keyword in messages should appear.</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>High / High</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>CS_093</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Search - Text Match</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Text message exists</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Verify text message found by content</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for text message content</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>Text message found in results</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>CS_094</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Search - User Match</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>User exists</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>Verify user/conversation found by name</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for user name</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>User conversation found in results</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>CS_095</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Search - Group Match</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Group exists</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Verify group found by name</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for group name</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>Group conversation found in results</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>CS_096</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Search - No Match</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>No matching content</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>Verify no results for non-existent query</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>1. Search for random string</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>Empty state shown</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
     </row>
